--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26339,6 +26339,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1130">
+      <c r="A1130" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1130" t="n">
+        <v>19202</v>
+      </c>
+      <c r="C1130" t="n">
+        <v>0.483000010251999</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>0.465999990701675</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>0.476999998092651</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>0.481000006198883</v>
+      </c>
+      <c r="G1130" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26362,6 +26362,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1131">
+      <c r="A1131" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1131" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1131" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="G1131" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26385,6 +26385,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1132">
+      <c r="A1132" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1132" t="n">
+        <v>29250</v>
+      </c>
+      <c r="C1132" t="n">
+        <v>0.47299998998642</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>0.46000000834465</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>0.467000007629395</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>0.47299998998642</v>
+      </c>
+      <c r="G1132" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26408,6 +26408,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1133">
+      <c r="A1133" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1133" t="n">
+        <v>34506</v>
+      </c>
+      <c r="C1133" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>0.448000013828278</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>0.460999995470047</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="G1133" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26249,22 +26249,22 @@
     </row>
     <row r="1126">
       <c r="A1126" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1126" t="n">
-        <v>32323</v>
+        <v>11848</v>
       </c>
       <c r="C1126" t="n">
-        <v>0.490000009536743</v>
+        <v>0.495000004768372</v>
       </c>
       <c r="D1126" t="n">
-        <v>0.467000007629395</v>
+        <v>0.479999989271164</v>
       </c>
       <c r="E1126" t="n">
-        <v>0.476000010967255</v>
+        <v>0.495000004768372</v>
       </c>
       <c r="F1126" t="n">
-        <v>0.470999985933304</v>
+        <v>0.479999989271164</v>
       </c>
       <c r="G1126" t="s">
         <v>7</v>
@@ -26272,22 +26272,22 @@
     </row>
     <row r="1127">
       <c r="A1127" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1127" t="n">
-        <v>21195</v>
+        <v>32323</v>
       </c>
       <c r="C1127" t="n">
-        <v>0.472000002861023</v>
+        <v>0.490000009536743</v>
       </c>
       <c r="D1127" t="n">
-        <v>0.465000003576279</v>
+        <v>0.467000007629395</v>
       </c>
       <c r="E1127" t="n">
-        <v>0.472000002861023</v>
+        <v>0.476000010967255</v>
       </c>
       <c r="F1127" t="n">
-        <v>0.469999998807907</v>
+        <v>0.470999985933304</v>
       </c>
       <c r="G1127" t="s">
         <v>7</v>
@@ -26295,22 +26295,22 @@
     </row>
     <row r="1128">
       <c r="A1128" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1128" t="n">
-        <v>46376</v>
+        <v>21195</v>
       </c>
       <c r="C1128" t="n">
-        <v>0.485000014305115</v>
+        <v>0.472000002861023</v>
       </c>
       <c r="D1128" t="n">
-        <v>0.458000004291534</v>
+        <v>0.465000003576279</v>
       </c>
       <c r="E1128" t="n">
-        <v>0.458999991416931</v>
+        <v>0.472000002861023</v>
       </c>
       <c r="F1128" t="n">
-        <v>0.485000014305115</v>
+        <v>0.469999998807907</v>
       </c>
       <c r="G1128" t="s">
         <v>7</v>
@@ -26318,22 +26318,22 @@
     </row>
     <row r="1129">
       <c r="A1129" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1129" t="n">
-        <v>15940</v>
+        <v>46376</v>
       </c>
       <c r="C1129" t="n">
-        <v>0.488999992609024</v>
+        <v>0.485000014305115</v>
       </c>
       <c r="D1129" t="n">
-        <v>0.479999989271164</v>
+        <v>0.458000004291534</v>
       </c>
       <c r="E1129" t="n">
+        <v>0.458999991416931</v>
+      </c>
+      <c r="F1129" t="n">
         <v>0.485000014305115</v>
-      </c>
-      <c r="F1129" t="n">
-        <v>0.488999992609024</v>
       </c>
       <c r="G1129" t="s">
         <v>7</v>
@@ -26341,22 +26341,22 @@
     </row>
     <row r="1130">
       <c r="A1130" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1130" t="n">
-        <v>19202</v>
+        <v>15940</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.483000010251999</v>
+        <v>0.488999992609024</v>
       </c>
       <c r="D1130" t="n">
-        <v>0.465999990701675</v>
+        <v>0.479999989271164</v>
       </c>
       <c r="E1130" t="n">
-        <v>0.476999998092651</v>
+        <v>0.485000014305115</v>
       </c>
       <c r="F1130" t="n">
-        <v>0.481000006198883</v>
+        <v>0.488999992609024</v>
       </c>
       <c r="G1130" t="s">
         <v>7</v>
@@ -26364,22 +26364,22 @@
     </row>
     <row r="1131">
       <c r="A1131" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1131" t="n">
-        <v>5000</v>
+        <v>19202</v>
       </c>
       <c r="C1131" t="n">
-        <v>0.469999998807907</v>
+        <v>0.483000010251999</v>
       </c>
       <c r="D1131" t="n">
-        <v>0.469999998807907</v>
+        <v>0.465999990701675</v>
       </c>
       <c r="E1131" t="n">
-        <v>0.469999998807907</v>
+        <v>0.476999998092651</v>
       </c>
       <c r="F1131" t="n">
-        <v>0.469999998807907</v>
+        <v>0.481000006198883</v>
       </c>
       <c r="G1131" t="s">
         <v>7</v>
@@ -26387,22 +26387,22 @@
     </row>
     <row r="1132">
       <c r="A1132" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1132" t="n">
-        <v>29250</v>
+        <v>5000</v>
       </c>
       <c r="C1132" t="n">
-        <v>0.47299998998642</v>
+        <v>0.469999998807907</v>
       </c>
       <c r="D1132" t="n">
-        <v>0.46000000834465</v>
+        <v>0.469999998807907</v>
       </c>
       <c r="E1132" t="n">
-        <v>0.467000007629395</v>
+        <v>0.469999998807907</v>
       </c>
       <c r="F1132" t="n">
-        <v>0.47299998998642</v>
+        <v>0.469999998807907</v>
       </c>
       <c r="G1132" t="s">
         <v>7</v>
@@ -26410,22 +26410,22 @@
     </row>
     <row r="1133">
       <c r="A1133" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1133" t="n">
-        <v>34506</v>
+        <v>29250</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.469999998807907</v>
+        <v>0.47299998998642</v>
       </c>
       <c r="D1133" t="n">
-        <v>0.448000013828278</v>
+        <v>0.46000000834465</v>
       </c>
       <c r="E1133" t="n">
-        <v>0.460999995470047</v>
+        <v>0.467000007629395</v>
       </c>
       <c r="F1133" t="n">
-        <v>0.462000012397766</v>
+        <v>0.47299998998642</v>
       </c>
       <c r="G1133" t="s">
         <v>7</v>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -29911,6 +29911,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1137">
+      <c r="A1137" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1137" t="n">
+        <v>37860</v>
+      </c>
+      <c r="C1137" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>0.472000002861023</v>
+      </c>
+      <c r="H1137" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -29937,6 +29937,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1138">
+      <c r="A1138" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1138" t="n">
+        <v>23666</v>
+      </c>
+      <c r="C1138" t="n">
+        <v>0.479000002145767</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>0.460999995470047</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>0.479000002145767</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="G1138" t="n">
+        <v>0.474999994039536</v>
+      </c>
+      <c r="H1138" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -29963,6 +29963,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1139">
+      <c r="A1139" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1139" t="n">
+        <v>1724</v>
+      </c>
+      <c r="C1139" t="n">
+        <v>0.462999999523163</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>0.462999999523163</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="G1139" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="H1139" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -29989,6 +29989,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1140">
+      <c r="A1140" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1140" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C1140" t="n">
+        <v>0.46399998664856</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>0.45100000500679</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="G1140" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="H1140" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -30067,6 +30067,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1143">
+      <c r="A1143" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1143" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C1143" t="n">
+        <v>0.453000009059906</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>0.430999994277954</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>0.44200000166893</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>0.453000009059906</v>
+      </c>
+      <c r="G1143" t="n">
+        <v>0.453000009059906</v>
+      </c>
+      <c r="H1143" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26715,7 +26715,7 @@
         <v>2487</v>
       </c>
       <c r="C1146" t="n">
-        <v>0.448000013828278</v>
+        <v>0.458999991416931</v>
       </c>
       <c r="D1146" t="n">
         <v>0.446999996900558</v>
@@ -26723,8 +26723,31 @@
       <c r="E1146" t="n">
         <v>0.448000013828278</v>
       </c>
-      <c r="F1146"/>
+      <c r="F1146" t="n">
+        <v>0.458999991416931</v>
+      </c>
       <c r="G1146" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1147" t="n">
+        <v>11063</v>
+      </c>
+      <c r="C1147" t="n">
+        <v>0.458999991416931</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>0.448000013828278</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="F1147"/>
+      <c r="G1147" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26746,8 +26746,31 @@
       <c r="E1147" t="n">
         <v>0.449999988079071</v>
       </c>
-      <c r="F1147"/>
+      <c r="F1147" t="n">
+        <v>0.448000013828278</v>
+      </c>
       <c r="G1147" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1148" t="n">
+        <v>6579</v>
+      </c>
+      <c r="C1148" t="n">
+        <v>0.456000000238419</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>0.442999988794327</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>0.453000009059906</v>
+      </c>
+      <c r="F1148"/>
+      <c r="G1148" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26769,7 +26769,9 @@
       <c r="E1148" t="n">
         <v>0.453000009059906</v>
       </c>
-      <c r="F1148"/>
+      <c r="F1148" t="n">
+        <v>0.456000000238419</v>
+      </c>
       <c r="G1148" t="s">
         <v>7</v>
       </c>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26776,6 +26776,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1149">
+      <c r="A1149" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1149" t="n">
+        <v>0.456000000238419</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>0.456000000238419</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>0.456000000238419</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>0.456000000238419</v>
+      </c>
+      <c r="G1149" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1150" t="n">
+        <v>10280</v>
+      </c>
+      <c r="C1150" t="n">
+        <v>0.46399998664856</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>0.448000013828278</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>0.455000013113022</v>
+      </c>
+      <c r="F1150"/>
+      <c r="G1150" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -26822,6 +26822,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1151">
+      <c r="A1151" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1151" t="n">
+        <v>37495</v>
+      </c>
+      <c r="C1151" t="n">
+        <v>0.476999998092651</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>0.44200000166893</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>0.449000000953674</v>
+      </c>
+      <c r="G1151" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -30353,6 +30353,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1154">
+      <c r="A1154" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1154" t="n">
+        <v>85987</v>
+      </c>
+      <c r="C1154" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>0.42399999499321</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="G1154" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="H1154" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -30364,7 +30364,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="D1154" t="n">
-        <v>0.42399999499321</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="E1154" t="n">
         <v>0.449999988079071</v>
@@ -30376,6 +30376,32 @@
         <v>0.412000000476837</v>
       </c>
       <c r="H1154" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1155" t="n">
+        <v>20721</v>
+      </c>
+      <c r="C1155" t="n">
+        <v>0.428999990224838</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>0.412999987602234</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>0.412999987602234</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="G1155" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="H1155" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -33902,6 +33902,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1157">
+      <c r="A1157" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1157" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1157" t="n">
+        <v>0.412999987602234</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G1157" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>143996</v>
+      </c>
+      <c r="I1157" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -33931,6 +33931,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1158">
+      <c r="A1158" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1158" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1158" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>0.423000007867813</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="G1158" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>117460</v>
+      </c>
+      <c r="I1158" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -33960,6 +33960,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1159">
+      <c r="A1159" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1159" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1159" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>0.439000010490417</v>
+      </c>
+      <c r="G1159" t="n">
+        <v>0.439000010490417</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>16382</v>
+      </c>
+      <c r="I1159" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -33989,6 +33989,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1160">
+      <c r="A1160" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1160" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>0.444000005722046</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>0.444000005722046</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="G1160" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>29439</v>
+      </c>
+      <c r="I1160" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -34018,6 +34018,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1161">
+      <c r="A1161" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1161" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>0.41499999165535</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>0.41499999165535</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="G1161" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>6975</v>
+      </c>
+      <c r="I1161" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -34047,6 +34047,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1162">
+      <c r="A1162" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1162" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1162" t="n">
+        <v>0.409000009298325</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>0.412999987602234</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>0.391000002622604</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>90785</v>
+      </c>
+      <c r="I1162" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -34061,7 +34061,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="E1162" t="n">
-        <v>0.391000002622604</v>
+        <v>0.389999985694885</v>
       </c>
       <c r="F1162" t="n">
         <v>0.398000001907349</v>
@@ -34073,6 +34073,35 @@
         <v>90785</v>
       </c>
       <c r="I1162" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1163" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1163" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>14783</v>
+      </c>
+      <c r="I1163" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -34105,6 +34105,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1164">
+      <c r="A1164" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1164" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1164" t="n">
+        <v>0.405000001192093</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>0.405000001192093</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>0.39300000667572</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="G1164" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>37872</v>
+      </c>
+      <c r="I1164" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COSMO.MI.xlsx
+++ b/data/COSMO.MI.xlsx
@@ -34134,6 +34134,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1165">
+      <c r="A1165" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1165" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1165" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>0.395000010728836</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="G1165" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>10600</v>
+      </c>
+      <c r="I1165" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
